--- a/summary_report.xlsx
+++ b/summary_report.xlsx
@@ -775,7 +775,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TKT-20260313-823BF735</t>
+          <t>TKT-20260313-55B27524</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TKT-20260313-97C7735D</t>
+          <t>TKT-20260313-9A656B8D</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TKT-20260313-42A61208</t>
+          <t>TKT-20260313-97DA11B6</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TKT-20260313-62C18086</t>
+          <t>TKT-20260313-E63CE9EA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TKT-20260313-40393A51</t>
+          <t>TKT-20260313-E15A2B12</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TKT-20260313-F5FEB105</t>
+          <t>TKT-20260313-2FE9108C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TKT-20260313-336F4C89</t>
+          <t>TKT-20260313-55D9C069</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TKT-20260313-AE1CA474</t>
+          <t>TKT-20260313-88B57D25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1191,7 +1191,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TKT-20260313-F6C88436</t>
+          <t>TKT-20260313-12DEB8CB</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TKT-20260313-D520E809</t>
+          <t>TKT-20260313-2A87160C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TKT-20260313-273992B0</t>
+          <t>TKT-20260313-1F26A8B4</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>REJ-20260313-F7B9D386</t>
+          <t>REJ-20260313-CE381147</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REJ-20260313-E05EECBD</t>
+          <t>REJ-20260313-480D6943</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1513,7 +1513,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>REJ-20260313-C994CE45</t>
+          <t>REJ-20260313-5DC0B7CC</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Unknown issue type: 'unknown' (allowed: hardware, software, login, other, wifi)</t>
+          <t>Unknown issue type: 'unknown' (allowed: wifi, hardware, login, software, other)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REJ-20260313-7AB209E5</t>
+          <t>REJ-20260313-0DEC4342</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>REJ-20260313-65F58BE4</t>
+          <t>REJ-20260313-6BAB6A30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
